--- a/output/prediksi/akurasi_realisasi.xlsx
+++ b/output/prediksi/akurasi_realisasi.xlsx
@@ -15987,7 +15987,7 @@
         <v>78.27500000000001</v>
       </c>
       <c r="H269">
-        <v>76.033</v>
+        <v>76.03</v>
       </c>
       <c r="I269">
         <v>9</v>
@@ -16002,10 +16002,10 @@
         <v>0</v>
       </c>
       <c r="M269">
-        <v>2.242</v>
+        <v>2.245</v>
       </c>
       <c r="N269">
-        <v>2.242</v>
+        <v>2.245</v>
       </c>
       <c r="O269" t="s">
         <v>447</v>
@@ -32099,7 +32099,7 @@
         <v>107.158</v>
       </c>
       <c r="H573">
-        <v>99.949</v>
+        <v>99.955</v>
       </c>
       <c r="I573">
         <v>9</v>
@@ -32114,10 +32114,10 @@
         <v>0</v>
       </c>
       <c r="M573">
-        <v>7.209</v>
+        <v>7.203</v>
       </c>
       <c r="N573">
-        <v>7.209</v>
+        <v>7.203</v>
       </c>
       <c r="O573" t="s">
         <v>448</v>
@@ -41003,7 +41003,7 @@
         <v>368.648</v>
       </c>
       <c r="H741">
-        <v>367.812</v>
+        <v>367.781</v>
       </c>
       <c r="I741">
         <v>9</v>
@@ -41018,10 +41018,10 @@
         <v>0</v>
       </c>
       <c r="M741">
-        <v>0.836</v>
+        <v>0.867</v>
       </c>
       <c r="N741">
-        <v>0.836</v>
+        <v>0.867</v>
       </c>
       <c r="O741" t="s">
         <v>447</v>
@@ -41427,7 +41427,7 @@
         <v>366.14</v>
       </c>
       <c r="H749">
-        <v>366.252</v>
+        <v>366.251</v>
       </c>
       <c r="I749">
         <v>9</v>
@@ -41442,10 +41442,10 @@
         <v>0</v>
       </c>
       <c r="M749">
-        <v>-0.112</v>
+        <v>-0.111</v>
       </c>
       <c r="N749">
-        <v>0.112</v>
+        <v>0.111</v>
       </c>
       <c r="O749" t="s">
         <v>449</v>
@@ -47257,7 +47257,7 @@
         <v>116.624</v>
       </c>
       <c r="H859">
-        <v>114.661</v>
+        <v>114.531</v>
       </c>
       <c r="I859">
         <v>9</v>
@@ -47272,10 +47272,10 @@
         <v>0</v>
       </c>
       <c r="M859">
-        <v>1.963</v>
+        <v>2.093</v>
       </c>
       <c r="N859">
-        <v>1.963</v>
+        <v>2.093</v>
       </c>
       <c r="O859" t="s">
         <v>447</v>
@@ -48317,7 +48317,7 @@
         <v>120.97</v>
       </c>
       <c r="H879">
-        <v>119.49</v>
+        <v>119.484</v>
       </c>
       <c r="I879">
         <v>9</v>
@@ -48332,10 +48332,10 @@
         <v>0</v>
       </c>
       <c r="M879">
-        <v>1.48</v>
+        <v>1.486</v>
       </c>
       <c r="N879">
-        <v>1.48</v>
+        <v>1.486</v>
       </c>
       <c r="O879" t="s">
         <v>448</v>
@@ -48529,7 +48529,7 @@
         <v>162.937</v>
       </c>
       <c r="H883">
-        <v>161.947</v>
+        <v>161.948</v>
       </c>
       <c r="I883">
         <v>9</v>
@@ -48544,10 +48544,10 @@
         <v>0</v>
       </c>
       <c r="M883">
-        <v>0.99</v>
+        <v>0.989</v>
       </c>
       <c r="N883">
-        <v>0.99</v>
+        <v>0.989</v>
       </c>
       <c r="O883" t="s">
         <v>447</v>
@@ -48741,7 +48741,7 @@
         <v>149.099</v>
       </c>
       <c r="H887">
-        <v>131.465</v>
+        <v>131.459</v>
       </c>
       <c r="I887">
         <v>9</v>
@@ -48756,10 +48756,10 @@
         <v>0</v>
       </c>
       <c r="M887">
-        <v>17.634</v>
+        <v>17.64</v>
       </c>
       <c r="N887">
-        <v>17.634</v>
+        <v>17.64</v>
       </c>
       <c r="O887" t="s">
         <v>449</v>
@@ -48953,7 +48953,7 @@
         <v>164.548</v>
       </c>
       <c r="H891">
-        <v>160.779</v>
+        <v>160.777</v>
       </c>
       <c r="I891">
         <v>9</v>
@@ -48968,10 +48968,10 @@
         <v>0</v>
       </c>
       <c r="M891">
-        <v>3.769</v>
+        <v>3.771</v>
       </c>
       <c r="N891">
-        <v>3.769</v>
+        <v>3.771</v>
       </c>
       <c r="O891" t="s">
         <v>447</v>
@@ -49165,7 +49165,7 @@
         <v>70.648</v>
       </c>
       <c r="H895">
-        <v>69.70999999999999</v>
+        <v>69.712</v>
       </c>
       <c r="I895">
         <v>9</v>
@@ -49180,10 +49180,10 @@
         <v>0</v>
       </c>
       <c r="M895">
-        <v>0.9379999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="N895">
-        <v>0.9379999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="O895" t="s">
         <v>447</v>
@@ -49377,7 +49377,7 @@
         <v>198.086</v>
       </c>
       <c r="H899">
-        <v>197.832</v>
+        <v>197.836</v>
       </c>
       <c r="I899">
         <v>9</v>
@@ -49392,10 +49392,10 @@
         <v>0</v>
       </c>
       <c r="M899">
-        <v>0.254</v>
+        <v>0.25</v>
       </c>
       <c r="N899">
-        <v>0.254</v>
+        <v>0.25</v>
       </c>
       <c r="O899" t="s">
         <v>447</v>
@@ -62733,7 +62733,7 @@
         <v>76.815</v>
       </c>
       <c r="H1151">
-        <v>76.033</v>
+        <v>76.03</v>
       </c>
       <c r="I1151">
         <v>9</v>
@@ -62748,10 +62748,10 @@
         <v>0</v>
       </c>
       <c r="M1151">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="N1151">
-        <v>0.782</v>
+        <v>0.785</v>
       </c>
       <c r="O1151" t="s">
         <v>447</v>
@@ -70789,7 +70789,7 @@
         <v>105.665</v>
       </c>
       <c r="H1303">
-        <v>99.949</v>
+        <v>99.955</v>
       </c>
       <c r="I1303">
         <v>9</v>
@@ -70804,10 +70804,10 @@
         <v>0</v>
       </c>
       <c r="M1303">
-        <v>5.716</v>
+        <v>5.71</v>
       </c>
       <c r="N1303">
-        <v>5.716</v>
+        <v>5.71</v>
       </c>
       <c r="O1303" t="s">
         <v>448</v>
@@ -75241,7 +75241,7 @@
         <v>370.766</v>
       </c>
       <c r="H1387">
-        <v>367.812</v>
+        <v>367.781</v>
       </c>
       <c r="I1387">
         <v>9</v>
@@ -75256,10 +75256,10 @@
         <v>0</v>
       </c>
       <c r="M1387">
-        <v>2.954</v>
+        <v>2.985</v>
       </c>
       <c r="N1387">
-        <v>2.954</v>
+        <v>2.985</v>
       </c>
       <c r="O1387" t="s">
         <v>447</v>
@@ -75453,7 +75453,7 @@
         <v>366.974</v>
       </c>
       <c r="H1391">
-        <v>366.252</v>
+        <v>366.251</v>
       </c>
       <c r="I1391">
         <v>9</v>
@@ -75468,10 +75468,10 @@
         <v>0</v>
       </c>
       <c r="M1391">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="N1391">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="O1391" t="s">
         <v>447</v>
@@ -78368,7 +78368,7 @@
         <v>117.192</v>
       </c>
       <c r="H1446">
-        <v>114.661</v>
+        <v>114.531</v>
       </c>
       <c r="I1446">
         <v>9</v>
@@ -78383,10 +78383,10 @@
         <v>0</v>
       </c>
       <c r="M1446">
-        <v>2.531</v>
+        <v>2.661</v>
       </c>
       <c r="N1446">
-        <v>2.531</v>
+        <v>2.661</v>
       </c>
       <c r="O1446" t="s">
         <v>447</v>
@@ -78898,7 +78898,7 @@
         <v>122.216</v>
       </c>
       <c r="H1456">
-        <v>119.49</v>
+        <v>119.484</v>
       </c>
       <c r="I1456">
         <v>9</v>
@@ -78913,10 +78913,10 @@
         <v>0</v>
       </c>
       <c r="M1456">
-        <v>2.726</v>
+        <v>2.732</v>
       </c>
       <c r="N1456">
-        <v>2.726</v>
+        <v>2.732</v>
       </c>
       <c r="O1456" t="s">
         <v>448</v>
@@ -79004,7 +79004,7 @@
         <v>162.436</v>
       </c>
       <c r="H1458">
-        <v>161.947</v>
+        <v>161.948</v>
       </c>
       <c r="I1458">
         <v>9</v>
@@ -79019,10 +79019,10 @@
         <v>0</v>
       </c>
       <c r="M1458">
-        <v>0.489</v>
+        <v>0.488</v>
       </c>
       <c r="N1458">
-        <v>0.489</v>
+        <v>0.488</v>
       </c>
       <c r="O1458" t="s">
         <v>447</v>
@@ -79110,7 +79110,7 @@
         <v>136.921</v>
       </c>
       <c r="H1460">
-        <v>131.465</v>
+        <v>131.459</v>
       </c>
       <c r="I1460">
         <v>9</v>
@@ -79125,10 +79125,10 @@
         <v>0</v>
       </c>
       <c r="M1460">
-        <v>5.456</v>
+        <v>5.462</v>
       </c>
       <c r="N1460">
-        <v>5.456</v>
+        <v>5.462</v>
       </c>
       <c r="O1460" t="s">
         <v>449</v>
@@ -79216,7 +79216,7 @@
         <v>161.559</v>
       </c>
       <c r="H1462">
-        <v>160.779</v>
+        <v>160.777</v>
       </c>
       <c r="I1462">
         <v>9</v>
@@ -79231,10 +79231,10 @@
         <v>0</v>
       </c>
       <c r="M1462">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="N1462">
-        <v>0.78</v>
+        <v>0.782</v>
       </c>
       <c r="O1462" t="s">
         <v>449</v>
@@ -79322,7 +79322,7 @@
         <v>69.172</v>
       </c>
       <c r="H1464">
-        <v>69.70999999999999</v>
+        <v>69.712</v>
       </c>
       <c r="I1464">
         <v>9</v>
@@ -79337,10 +79337,10 @@
         <v>0</v>
       </c>
       <c r="M1464">
-        <v>-0.538</v>
+        <v>-0.54</v>
       </c>
       <c r="N1464">
-        <v>0.538</v>
+        <v>0.54</v>
       </c>
       <c r="O1464" t="s">
         <v>447</v>
@@ -79428,7 +79428,7 @@
         <v>197.492</v>
       </c>
       <c r="H1466">
-        <v>197.832</v>
+        <v>197.836</v>
       </c>
       <c r="I1466">
         <v>9</v>
@@ -79443,10 +79443,10 @@
         <v>0</v>
       </c>
       <c r="M1466">
-        <v>-0.34</v>
+        <v>-0.344</v>
       </c>
       <c r="N1466">
-        <v>0.34</v>
+        <v>0.344</v>
       </c>
       <c r="O1466" t="s">
         <v>447</v>
@@ -83988,10 +83988,10 @@
         <v>4</v>
       </c>
       <c r="F44">
-        <v>1.887</v>
+        <v>1.888</v>
       </c>
       <c r="G44">
-        <v>1.887</v>
+        <v>1.888</v>
       </c>
       <c r="H44">
         <v>2</v>
@@ -84820,10 +84820,10 @@
         <v>4</v>
       </c>
       <c r="F70">
-        <v>0.659</v>
+        <v>0.66</v>
       </c>
       <c r="G70">
-        <v>0.478</v>
+        <v>0.479</v>
       </c>
       <c r="H70">
         <v>3</v>
@@ -84884,10 +84884,10 @@
         <v>4</v>
       </c>
       <c r="F72">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="G72">
-        <v>0.248</v>
+        <v>0.247</v>
       </c>
       <c r="H72">
         <v>3</v>
@@ -85300,10 +85300,10 @@
         <v>4</v>
       </c>
       <c r="F85">
-        <v>13.97</v>
+        <v>13.971</v>
       </c>
       <c r="G85">
-        <v>13.97</v>
+        <v>13.971</v>
       </c>
       <c r="H85">
         <v>4</v>
@@ -85844,10 +85844,10 @@
         <v>4</v>
       </c>
       <c r="F102">
-        <v>1.728</v>
+        <v>1.76</v>
       </c>
       <c r="G102">
-        <v>1.728</v>
+        <v>1.76</v>
       </c>
       <c r="H102">
         <v>4</v>
@@ -86260,10 +86260,10 @@
         <v>4</v>
       </c>
       <c r="F115">
-        <v>1.374</v>
+        <v>1.382</v>
       </c>
       <c r="G115">
-        <v>-0.956</v>
+        <v>-0.948</v>
       </c>
       <c r="H115">
         <v>4</v>
@@ -86516,10 +86516,10 @@
         <v>4</v>
       </c>
       <c r="F123">
-        <v>1.058</v>
+        <v>1.057</v>
       </c>
       <c r="G123">
-        <v>1.058</v>
+        <v>1.057</v>
       </c>
       <c r="H123">
         <v>4</v>
@@ -88468,10 +88468,10 @@
         <v>4</v>
       </c>
       <c r="F184">
-        <v>0.248</v>
+        <v>0.247</v>
       </c>
       <c r="G184">
-        <v>-0.248</v>
+        <v>-0.247</v>
       </c>
       <c r="H184">
         <v>4</v>
@@ -89812,10 +89812,10 @@
         <v>2</v>
       </c>
       <c r="F226">
-        <v>0.5679999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="G226">
-        <v>0.5679999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="H226">
         <v>0</v>
@@ -90036,10 +90036,10 @@
         <v>2</v>
       </c>
       <c r="F233">
-        <v>2.156</v>
+        <v>2.158</v>
       </c>
       <c r="G233">
-        <v>2.156</v>
+        <v>2.158</v>
       </c>
       <c r="H233">
         <v>1</v>
@@ -90708,10 +90708,10 @@
         <v>2</v>
       </c>
       <c r="F254">
-        <v>4.944</v>
+        <v>4.947</v>
       </c>
       <c r="G254">
-        <v>4.944</v>
+        <v>4.947</v>
       </c>
       <c r="H254">
         <v>2</v>
@@ -90740,10 +90740,10 @@
         <v>3</v>
       </c>
       <c r="F255">
-        <v>4.19</v>
+        <v>4.188</v>
       </c>
       <c r="G255">
-        <v>4.19</v>
+        <v>4.188</v>
       </c>
       <c r="H255">
         <v>3</v>
@@ -91092,10 +91092,10 @@
         <v>2</v>
       </c>
       <c r="F266">
-        <v>2.083</v>
+        <v>2.148</v>
       </c>
       <c r="G266">
-        <v>2.083</v>
+        <v>2.148</v>
       </c>
       <c r="H266">
         <v>2</v>
@@ -91156,10 +91156,10 @@
         <v>2</v>
       </c>
       <c r="F268">
-        <v>1.966</v>
+        <v>1.982</v>
       </c>
       <c r="G268">
-        <v>1.966</v>
+        <v>1.982</v>
       </c>
       <c r="H268">
         <v>2</v>
@@ -92372,10 +92372,10 @@
         <v>2</v>
       </c>
       <c r="F306">
-        <v>0.827</v>
+        <v>0.828</v>
       </c>
       <c r="G306">
-        <v>0.827</v>
+        <v>0.828</v>
       </c>
       <c r="H306">
         <v>2</v>
@@ -93236,10 +93236,10 @@
         <v>2</v>
       </c>
       <c r="F333">
-        <v>0.5659999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="G333">
-        <v>0.5659999999999999</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H333">
         <v>2</v>
@@ -93524,10 +93524,10 @@
         <v>2</v>
       </c>
       <c r="F342">
-        <v>0.493</v>
+        <v>0.495</v>
       </c>
       <c r="G342">
-        <v>-0.493</v>
+        <v>-0.495</v>
       </c>
       <c r="H342">
         <v>2</v>
@@ -94100,10 +94100,10 @@
         <v>2</v>
       </c>
       <c r="F360">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="G360">
-        <v>-0.367</v>
+        <v>-0.368</v>
       </c>
       <c r="H360">
         <v>2</v>
@@ -94324,10 +94324,10 @@
         <v>2</v>
       </c>
       <c r="F367">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="G367">
-        <v>0.34</v>
+        <v>0.339</v>
       </c>
       <c r="H367">
         <v>2</v>
@@ -96131,7 +96131,7 @@
         <v>1.04</v>
       </c>
       <c r="E3">
-        <v>0.632</v>
+        <v>0.633</v>
       </c>
       <c r="F3">
         <v>86.40000000000001</v>
